--- a/Ficheiros EXCEL/GeoRoutePlan_Novo.xlsx
+++ b/Ficheiros EXCEL/GeoRoutePlan_Novo.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02485043-E85A-4795-881F-48D9E20CB4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Armazéns" sheetId="1" r:id="rId1"/>
